--- a/data/availability/projects/palm-hills-developments/palm-hills-ritz-carlton.xlsx
+++ b/data/availability/projects/palm-hills-developments/palm-hills-ritz-carlton.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -709,7 +709,6 @@
       <c r="G2" t="n">
         <v>375.5</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -720,7 +719,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
